--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2678"/>
+  <dimension ref="A1:E2679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -72719,6 +72731,33 @@
       <c r="E2678" t="inlineStr">
         <is>
           <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2679">
+      <c r="A2679" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2679" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2679" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D2679" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E2679" t="inlineStr">
+        <is>
+          <t>57</t>
         </is>
       </c>
     </row>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2751"/>
+  <dimension ref="A1:E2755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74705,6 +74705,114 @@
         </is>
       </c>
     </row>
+    <row r="2752">
+      <c r="A2752" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2752" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2752" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D2752" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E2752" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2753" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2753" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D2753" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E2753" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2754" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2754" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D2754" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E2754" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="2755">
+      <c r="A2755" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2755" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2755" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D2755" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E2755" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2755"/>
+  <dimension ref="A1:E2756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74813,6 +74813,33 @@
         </is>
       </c>
     </row>
+    <row r="2756">
+      <c r="A2756" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B2756" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2756" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D2756" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E2756" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2756"/>
+  <dimension ref="A1:E2757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74840,6 +74840,33 @@
         </is>
       </c>
     </row>
+    <row r="2757">
+      <c r="A2757" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B2757" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2757" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D2757" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E2757" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2757"/>
+  <dimension ref="A1:E2758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74867,6 +74867,33 @@
         </is>
       </c>
     </row>
+    <row r="2758">
+      <c r="A2758" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2758" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2758" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D2758" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E2758" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2758"/>
+  <dimension ref="A1:E2759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74894,6 +74894,33 @@
         </is>
       </c>
     </row>
+    <row r="2759">
+      <c r="A2759" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2759" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2759" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D2759" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E2759" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2759"/>
+  <dimension ref="A1:E2760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74921,6 +74921,33 @@
         </is>
       </c>
     </row>
+    <row r="2760">
+      <c r="A2760" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2760" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2760" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D2760" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E2760" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2760"/>
+  <dimension ref="A1:E2761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74948,6 +74948,33 @@
         </is>
       </c>
     </row>
+    <row r="2761">
+      <c r="A2761" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2761" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2761" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D2761" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E2761" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2761"/>
+  <dimension ref="A1:E2762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74975,6 +74975,33 @@
         </is>
       </c>
     </row>
+    <row r="2762">
+      <c r="A2762" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2762" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2762" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D2762" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E2762" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2762"/>
+  <dimension ref="A1:E2763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75002,6 +75002,33 @@
         </is>
       </c>
     </row>
+    <row r="2763">
+      <c r="A2763" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2763" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2763" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D2763" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E2763" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2763"/>
+  <dimension ref="A1:E2764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75029,6 +75029,33 @@
         </is>
       </c>
     </row>
+    <row r="2764">
+      <c r="A2764" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2764" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2764" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D2764" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E2764" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2764"/>
+  <dimension ref="A1:E2765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75056,6 +75056,33 @@
         </is>
       </c>
     </row>
+    <row r="2765">
+      <c r="A2765" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2765" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2765" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D2765" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E2765" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2765"/>
+  <dimension ref="A1:E2766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75083,6 +75083,33 @@
         </is>
       </c>
     </row>
+    <row r="2766">
+      <c r="A2766" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2766" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2766" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D2766" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E2766" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
